--- a/data_execl/base_data/ActivityRewardConfig.xlsx
+++ b/data_execl/base_data/ActivityRewardConfig.xlsx
@@ -5471,14 +5471,14 @@
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
-          <t>16#2176</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F171" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I171" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J171" s="0" t="n">
         <v>33</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
-          <t>16#2176</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F172" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I172" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J172" s="0" t="n">
         <v>33</v>
@@ -5535,14 +5535,14 @@
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
-          <t>16#2176</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F173" s="0" t="n">
         <v>3</v>
       </c>
       <c r="I173" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J173" s="0" t="n">
         <v>33</v>
@@ -5567,14 +5567,14 @@
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
-          <t>16#2576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F174" s="0" t="n">
         <v>4</v>
       </c>
       <c r="I174" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J174" s="0" t="n">
         <v>33</v>
@@ -5599,14 +5599,14 @@
       </c>
       <c r="E175" s="0" t="inlineStr">
         <is>
-          <t>16#2576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F175" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I175" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J175" s="0" t="n">
         <v>33</v>
@@ -5631,14 +5631,14 @@
       </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
-          <t>16#2576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F176" s="0" t="n">
         <v>6</v>
       </c>
       <c r="I176" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J176" s="0" t="n">
         <v>33</v>
@@ -5663,14 +5663,14 @@
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
-          <t>16#3976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F177" s="0" t="n">
         <v>7</v>
       </c>
       <c r="I177" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J177" s="0" t="n">
         <v>33</v>
@@ -5695,14 +5695,14 @@
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
-          <t>16#3976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F178" s="0" t="n">
         <v>8</v>
       </c>
       <c r="I178" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J178" s="0" t="n">
         <v>33</v>
@@ -5727,14 +5727,14 @@
       </c>
       <c r="E179" s="0" t="inlineStr">
         <is>
-          <t>16#3976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F179" s="0" t="n">
         <v>9</v>
       </c>
       <c r="I179" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J179" s="0" t="n">
         <v>33</v>
@@ -5759,14 +5759,14 @@
       </c>
       <c r="E180" s="0" t="inlineStr">
         <is>
-          <t>16#3976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F180" s="0" t="n">
         <v>10</v>
       </c>
       <c r="I180" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J180" s="0" t="n">
         <v>33</v>
@@ -5791,14 +5791,14 @@
       </c>
       <c r="E181" s="0" t="inlineStr">
         <is>
-          <t>16#2176</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F181" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I181" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J181" s="0" t="n">
         <v>33</v>
@@ -5823,14 +5823,14 @@
       </c>
       <c r="E182" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F182" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I182" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J182" s="0" t="n">
         <v>33</v>
@@ -5855,14 +5855,14 @@
       </c>
       <c r="E183" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F183" s="0" t="n">
         <v>3</v>
       </c>
       <c r="I183" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J183" s="0" t="n">
         <v>33</v>
@@ -5887,14 +5887,14 @@
       </c>
       <c r="E184" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F184" s="0" t="n">
         <v>4</v>
       </c>
       <c r="I184" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J184" s="0" t="n">
         <v>33</v>
@@ -5919,14 +5919,14 @@
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F185" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I185" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J185" s="0" t="n">
         <v>33</v>
@@ -5951,14 +5951,14 @@
       </c>
       <c r="E186" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F186" s="0" t="n">
         <v>6</v>
       </c>
       <c r="I186" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J186" s="0" t="n">
         <v>33</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F187" s="0" t="n">
         <v>7</v>
       </c>
       <c r="I187" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J187" s="0" t="n">
         <v>33</v>
@@ -6015,14 +6015,14 @@
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F188" s="0" t="n">
         <v>8</v>
       </c>
       <c r="I188" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J188" s="0" t="n">
         <v>33</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F189" s="0" t="n">
         <v>9</v>
       </c>
       <c r="I189" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J189" s="0" t="n">
         <v>33</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="E190" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F190" s="0" t="n">
         <v>10</v>
       </c>
       <c r="I190" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J190" s="0" t="n">
         <v>33</v>
@@ -6111,14 +6111,14 @@
       </c>
       <c r="E191" s="0" t="inlineStr">
         <is>
-          <t>16#2176</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F191" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J191" s="0" t="n">
         <v>33</v>
@@ -6143,14 +6143,14 @@
       </c>
       <c r="E192" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F192" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I192" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J192" s="0" t="n">
         <v>33</v>
@@ -6175,14 +6175,14 @@
       </c>
       <c r="E193" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F193" s="0" t="n">
         <v>3</v>
       </c>
       <c r="I193" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J193" s="0" t="n">
         <v>33</v>
@@ -6207,14 +6207,14 @@
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F194" s="0" t="n">
         <v>4</v>
       </c>
       <c r="I194" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J194" s="0" t="n">
         <v>33</v>
@@ -6239,14 +6239,14 @@
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F195" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I195" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J195" s="0" t="n">
         <v>33</v>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F196" s="0" t="n">
         <v>6</v>
       </c>
       <c r="I196" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J196" s="0" t="n">
         <v>33</v>
@@ -6303,14 +6303,14 @@
       </c>
       <c r="E197" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F197" s="0" t="n">
         <v>7</v>
       </c>
       <c r="I197" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J197" s="0" t="n">
         <v>33</v>
@@ -6335,14 +6335,14 @@
       </c>
       <c r="E198" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F198" s="0" t="n">
         <v>8</v>
       </c>
       <c r="I198" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J198" s="0" t="n">
         <v>33</v>
@@ -6367,14 +6367,14 @@
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F199" s="0" t="n">
         <v>9</v>
       </c>
       <c r="I199" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J199" s="0" t="n">
         <v>33</v>
@@ -6399,14 +6399,14 @@
       </c>
       <c r="E200" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F200" s="0" t="n">
         <v>10</v>
       </c>
       <c r="I200" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J200" s="0" t="n">
         <v>33</v>
@@ -6431,14 +6431,14 @@
       </c>
       <c r="E201" s="0" t="inlineStr">
         <is>
-          <t>16#2176</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F201" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J201" s="0" t="n">
         <v>33</v>
@@ -6463,14 +6463,14 @@
       </c>
       <c r="E202" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F202" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I202" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J202" s="0" t="n">
         <v>33</v>
@@ -6495,14 +6495,14 @@
       </c>
       <c r="E203" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F203" s="0" t="n">
         <v>3</v>
       </c>
       <c r="I203" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J203" s="0" t="n">
         <v>33</v>
@@ -6527,14 +6527,14 @@
       </c>
       <c r="E204" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F204" s="0" t="n">
         <v>4</v>
       </c>
       <c r="I204" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J204" s="0" t="n">
         <v>33</v>
@@ -6559,14 +6559,14 @@
       </c>
       <c r="E205" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F205" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I205" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J205" s="0" t="n">
         <v>33</v>
@@ -6591,14 +6591,14 @@
       </c>
       <c r="E206" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F206" s="0" t="n">
         <v>6</v>
       </c>
       <c r="I206" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J206" s="0" t="n">
         <v>33</v>
@@ -6623,14 +6623,14 @@
       </c>
       <c r="E207" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F207" s="0" t="n">
         <v>7</v>
       </c>
       <c r="I207" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J207" s="0" t="n">
         <v>33</v>
@@ -6655,14 +6655,14 @@
       </c>
       <c r="E208" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F208" s="0" t="n">
         <v>8</v>
       </c>
       <c r="I208" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J208" s="0" t="n">
         <v>33</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="E209" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F209" s="0" t="n">
         <v>9</v>
       </c>
       <c r="I209" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J209" s="0" t="n">
         <v>33</v>
@@ -6719,14 +6719,14 @@
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F210" s="0" t="n">
         <v>10</v>
       </c>
       <c r="I210" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J210" s="0" t="n">
         <v>33</v>
@@ -6751,14 +6751,14 @@
       </c>
       <c r="E211" s="0" t="inlineStr">
         <is>
-          <t>16#2176</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F211" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I211" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J211" s="0" t="n">
         <v>33</v>
@@ -6783,14 +6783,14 @@
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F212" s="0" t="n">
         <v>2</v>
       </c>
       <c r="I212" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J212" s="0" t="n">
         <v>33</v>
@@ -6815,14 +6815,14 @@
       </c>
       <c r="E213" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F213" s="0" t="n">
         <v>3</v>
       </c>
       <c r="I213" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J213" s="0" t="n">
         <v>33</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="E214" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F214" s="0" t="n">
         <v>4</v>
       </c>
       <c r="I214" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J214" s="0" t="n">
         <v>33</v>
@@ -6879,14 +6879,14 @@
       </c>
       <c r="E215" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F215" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I215" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J215" s="0" t="n">
         <v>33</v>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="E216" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F216" s="0" t="n">
         <v>6</v>
       </c>
       <c r="I216" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J216" s="0" t="n">
         <v>33</v>
@@ -6943,14 +6943,14 @@
       </c>
       <c r="E217" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F217" s="0" t="n">
         <v>7</v>
       </c>
       <c r="I217" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J217" s="0" t="n">
         <v>33</v>
@@ -6975,14 +6975,14 @@
       </c>
       <c r="E218" s="0" t="inlineStr">
         <is>
-          <t>16#2976</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F218" s="0" t="n">
         <v>8</v>
       </c>
       <c r="I218" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J218" s="0" t="n">
         <v>33</v>
@@ -7007,14 +7007,14 @@
       </c>
       <c r="E219" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F219" s="0" t="n">
         <v>9</v>
       </c>
       <c r="I219" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J219" s="0" t="n">
         <v>33</v>
@@ -7039,14 +7039,14 @@
       </c>
       <c r="E220" s="0" t="inlineStr">
         <is>
-          <t>16#3576</t>
+          <t>16#2156</t>
         </is>
       </c>
       <c r="F220" s="0" t="n">
         <v>10</v>
       </c>
       <c r="I220" s="0" t="n">
-        <v>30000</v>
+        <v>21560</v>
       </c>
       <c r="J220" s="0" t="n">
         <v>33</v>

--- a/data_execl/base_data/ActivityRewardConfig.xlsx
+++ b/data_execl/base_data/ActivityRewardConfig.xlsx
@@ -4718,7 +4718,7 @@
       </c>
       <c r="E144" s="0" t="inlineStr">
         <is>
-          <t>60448#1|19#5</t>
+          <t>60448#1|19#3</t>
         </is>
       </c>
       <c r="F144" s="0" t="n">

--- a/data_execl/base_data/ActivityRewardConfig.xlsx
+++ b/data_execl/base_data/ActivityRewardConfig.xlsx
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E409" s="0" t="inlineStr">
         <is>
-          <t>6000110#1000</t>
+          <t>6000110#1000|19#2</t>
         </is>
       </c>
       <c r="F409" s="0" t="n">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="E410" s="0" t="inlineStr">
         <is>
-          <t>6000110#1000</t>
+          <t>6000110#1000|19#3</t>
         </is>
       </c>
       <c r="F410" s="0" t="n">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="E411" s="0" t="inlineStr">
         <is>
-          <t>6000110#1000</t>
+          <t>6000110#1000|19#2</t>
         </is>
       </c>
       <c r="F411" s="0" t="n">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="E412" s="0" t="inlineStr">
         <is>
-          <t>6000110#1000</t>
+          <t>6000110#1000|19#3</t>
         </is>
       </c>
       <c r="F412" s="0" t="n">
